--- a/DATA_DIPA/DIPA_2026.xlsx
+++ b/DATA_DIPA/DIPA_2026.xlsx
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>46083</v>
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>46073</v>
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>46083</v>
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>46073</v>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>46073</v>
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>46120</v>
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>46064</v>
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>46094</v>
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>46066</v>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>46066</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>46066</v>
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>46066</v>
@@ -1236,7 +1236,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>46066</v>
@@ -1296,7 +1296,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>46066</v>
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>45261</v>
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>45260</v>
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>45261</v>
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>46073</v>
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>46065</v>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>46091</v>
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>46072</v>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>46062</v>
@@ -1836,7 +1836,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>45628</v>
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>46120</v>
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>45992</v>
@@ -2016,7 +2016,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>46092</v>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>46120</v>
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>46071</v>
@@ -2196,7 +2196,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>46064</v>
@@ -2256,7 +2256,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>46072</v>
@@ -2316,7 +2316,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>46093</v>
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>46114</v>
@@ -2436,7 +2436,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>46091</v>
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D35" s="2" t="n">
         <v>46092</v>
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D36" s="2" t="n">
         <v>46076</v>
@@ -2616,7 +2616,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D37" s="2" t="n">
         <v>46065</v>
@@ -2676,7 +2676,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D38" s="2" t="n">
         <v>46120</v>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D39" s="2" t="n">
         <v>45628</v>
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D40" s="2" t="n">
         <v>46111</v>
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D41" s="2" t="n">
         <v>46094</v>
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D42" s="2" t="n">
         <v>46076</v>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D43" s="2" t="n">
         <v>46071</v>
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D44" s="2" t="n">
         <v>46076</v>
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D45" s="2" t="n">
         <v>45992</v>
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D46" s="2" t="n">
         <v>46064</v>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D47" s="2" t="n">
         <v>46030</v>
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D48" s="2" t="n">
         <v>45262</v>
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D49" s="2" t="n">
         <v>46120</v>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D50" s="2" t="n">
         <v>45262</v>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D51" s="2" t="n">
         <v>46119</v>
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D52" s="2" t="n">
         <v>46120</v>
@@ -3576,7 +3576,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D53" s="2" t="n">
         <v>46120</v>
@@ -3636,7 +3636,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D54" s="2" t="n">
         <v>46066</v>
@@ -3696,7 +3696,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D55" s="2" t="n">
         <v>45992</v>
@@ -3756,7 +3756,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D56" s="2" t="n">
         <v>46120</v>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D57" s="2" t="n">
         <v>46120</v>
@@ -3876,7 +3876,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D58" s="2" t="n">
         <v>46076</v>
@@ -3936,7 +3936,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D59" s="2" t="n">
         <v>46087</v>
@@ -3996,7 +3996,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D60" s="2" t="n">
         <v>46076</v>
@@ -4056,7 +4056,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D61" s="2" t="n">
         <v>46062</v>
@@ -4116,7 +4116,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D62" s="2" t="n">
         <v>46120</v>
@@ -4176,7 +4176,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D63" s="2" t="n">
         <v>45628</v>
@@ -4236,7 +4236,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D64" s="2" t="n">
         <v>46093</v>
@@ -4296,7 +4296,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D65" s="2" t="n">
         <v>46093</v>
@@ -4356,7 +4356,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D66" s="2" t="n">
         <v>46114</v>
@@ -4416,7 +4416,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D67" s="2" t="n">
         <v>46114</v>
@@ -4476,7 +4476,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D68" s="2" t="n">
         <v>46094</v>
@@ -4536,7 +4536,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D69" s="2" t="n">
         <v>46092</v>
@@ -4596,7 +4596,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D70" s="2" t="n">
         <v>46066</v>
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D71" s="2" t="n">
         <v>46059</v>
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D72" s="2" t="n">
         <v>46064</v>
@@ -4776,7 +4776,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D73" s="2" t="n">
         <v>46059</v>
@@ -4836,7 +4836,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D74" s="2" t="n">
         <v>46059</v>
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D75" s="2" t="n">
         <v>46022</v>
@@ -4956,7 +4956,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D76" s="2" t="n">
         <v>46120</v>
@@ -5016,7 +5016,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D77" s="2" t="n">
         <v>46120</v>
@@ -5076,7 +5076,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D78" s="2" t="n">
         <v>46120</v>
@@ -5136,7 +5136,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D79" s="2" t="n">
         <v>46067</v>

--- a/DATA_DIPA/DIPA_2026.xlsx
+++ b/DATA_DIPA/DIPA_2026.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SATKER 007130</t>
+          <t>007130 - KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -572,7 +572,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SATKER 007190</t>
+          <t>007190 - KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -632,7 +632,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SATKER 007208</t>
+          <t>007208 - KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -692,7 +692,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SATKER 098963</t>
+          <t>098963 - PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -752,7 +752,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SATKER 099228</t>
+          <t>099228 - PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -812,7 +812,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SATKER 111071</t>
+          <t>111071 - KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -872,7 +872,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SATKER 111079</t>
+          <t>111079 - BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SATKER 344894</t>
+          <t>344894 - RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -992,7 +992,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SATKER 401944</t>
+          <t>401944 - PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SATKER 401945</t>
+          <t>401945 - PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SATKER 402267</t>
+          <t>402267 - PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SATKER 402268</t>
+          <t>402268 - PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SATKER 403409</t>
+          <t>403409 - PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SATKER 403410</t>
+          <t>403410 - PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SATKER 406426</t>
+          <t>406426 - LAPAS KELAS IIB MUARA DUA</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SATKER 406472</t>
+          <t>406472 - RUMAH TAHANAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SATKER 406488</t>
+          <t>406488 - LAPAS KELAS IIB MARTAPURA</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SATKER 410574</t>
+          <t>410574 - KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SATKER 418456</t>
+          <t>418456 - KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SATKER 418457</t>
+          <t>418457 - KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SATKER 418458</t>
+          <t>418458 - KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SATKER 418459</t>
+          <t>418459 - KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SATKER 418461</t>
+          <t>418461 - KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SATKER 418462</t>
+          <t>418462 - MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SATKER 418471</t>
+          <t>418471 - MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SATKER 419006</t>
+          <t>419006 - SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SATKER 424245</t>
+          <t>424245 - MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SATKER 424967</t>
+          <t>424967 - MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SATKER 426050</t>
+          <t>426050 - MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SATKER 426066</t>
+          <t>426066 - MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SATKER 428258</t>
+          <t>428258 - BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SATKER 431142</t>
+          <t>431142 - KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SATKER 440502</t>
+          <t>440502 - KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SATKER 440503</t>
+          <t>440503 - KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SATKER 440504</t>
+          <t>440504 - KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SATKER 440505</t>
+          <t>440505 - KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SATKER 440506</t>
+          <t>440506 - KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SATKER 440507</t>
+          <t>440507 - KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SATKER 500163</t>
+          <t>500163 - KPPN BATURAJA PENYALUR DANA TRANSFER UMUM</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SATKER 527975</t>
+          <t>527975 - KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SATKER 553099</t>
+          <t>553099 - MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SATKER 553792</t>
+          <t>553792 - MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SATKER 574370</t>
+          <t>574370 - MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SATKER 597480</t>
+          <t>597480 - MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SATKER 597558</t>
+          <t>597558 - MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SATKER 600092</t>
+          <t>600092 - KPPN BATURAJA PENYALUR DANA TRANSFER KHUSUS</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SATKER 632013</t>
+          <t>632013 - BAPAS KELAS II OKU INDUK</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SATKER 641681</t>
+          <t>641681 - POLRES OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SATKER 653271</t>
+          <t>653271 - RUMAH PENYIMPANAN BENDA SITAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SATKER 656553</t>
+          <t>656553 - KPU  KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SATKER 656560</t>
+          <t>656560 - KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SATKER 656574</t>
+          <t>656574 - KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SATKER 661192</t>
+          <t>661192 - MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SATKER 662127</t>
+          <t>662127 - MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SATKER 665292</t>
+          <t>665292 - POLRES OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SATKER 665307</t>
+          <t>665307 - POLRES OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SATKER 666501</t>
+          <t>666501 - KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SATKER 666502</t>
+          <t>666502 - KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SATKER 666503</t>
+          <t>666503 - KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SATKER 666504</t>
+          <t>666504 - KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SATKER 666505</t>
+          <t>666505 - KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SATKER 666507</t>
+          <t>666507 - KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SATKER 667215</t>
+          <t>667215 - BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SATKER 668529</t>
+          <t>668529 - BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SATKER 669055</t>
+          <t>669055 - KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR PROV. SUMATRA SELATAN</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SATKER 670561</t>
+          <t>670561 - KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SATKER 685001</t>
+          <t>685001 - PUSLATPUR KODIKLATAD</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SATKER 686503</t>
+          <t>686503 - SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SATKER 690801</t>
+          <t>690801 - LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SATKER 692334</t>
+          <t>692334 - LAPAS KELAS II B MUARA DUA</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SATKER 692339</t>
+          <t>692339 - RUTAN KELAS II B BATURAJA</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SATKER 692340</t>
+          <t>692340 - LAPAS KELAS II B MARTAPURA</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SATKER 692625</t>
+          <t>692625 - BAPAS KELAS II OKU INDUK</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SATKER 692725</t>
+          <t>692725 - RUPBASAN KELAS II BATURAJA</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -4952,7 +4952,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SATKER 695176</t>
+          <t>695176 - KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SATKER 695182</t>
+          <t>695182 - KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SATKER 695184</t>
+          <t>695184 - KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SATKER 700283</t>
+          <t>700283 - KPPN BATURAJA PENYALUR DANA DESA, INSENTIF FISKAL, OTONOMI KHUSUS DAN KEISTIMEWAAN</t>
         </is>
       </c>
       <c r="C79" t="n">

--- a/DATA_DIPA/DIPA_2026.xlsx
+++ b/DATA_DIPA/DIPA_2026.xlsx
@@ -522,11 +522,11 @@
         <v>46387</v>
       </c>
       <c r="E2" t="n">
-        <v>9598408000</v>
+        <v>1831280000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Satker Besar</t>
+          <t>Satker Kecil</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -539,20 +539,20 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>A01</t>
+          <t>F00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>USULAN_DIPA_REVISI</t>
+          <t>REVISI_SABA</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>DIPA-006.01.2.007130/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
@@ -560,7 +560,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>4911848705617379</t>
+          <t>0988241741088915</t>
         </is>
       </c>
     </row>
@@ -582,11 +582,11 @@
         <v>46387</v>
       </c>
       <c r="E3" t="n">
-        <v>8132104000</v>
+        <v>2045231000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Satker Besar</t>
+          <t>Satker Sedang</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -599,20 +599,20 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>A01</t>
+          <t>F00</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>USULAN_DIPA_REVISI</t>
+          <t>REVISI_SABA</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>DIPA-006.01.2.007190/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
@@ -620,7 +620,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>9419677010459521</t>
+          <t>9480209042547146</t>
         </is>
       </c>
     </row>
@@ -642,11 +642,11 @@
         <v>46387</v>
       </c>
       <c r="E4" t="n">
-        <v>8257629000</v>
+        <v>1421411000</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Satker Besar</t>
+          <t>Satker Kecil</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -659,20 +659,20 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>A01</t>
+          <t>F00</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>USULAN_DIPA_REVISI</t>
+          <t>REVISI_SABA</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>DIPA-006.01.2.007208/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
@@ -680,7 +680,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>7045670640481044</t>
+          <t>2453411302768045</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
         <v>2026</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>45261</v>
+        <v>44938</v>
       </c>
       <c r="E16" t="n">
         <v>6270503000</v>
@@ -1396,7 +1396,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>45261</v>
+        <v>44938</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>2026</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>45261</v>
+        <v>44938</v>
       </c>
       <c r="E18" t="n">
         <v>8373512000</v>
@@ -1516,7 +1516,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>45261</v>
+        <v>44938</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1602,11 +1602,11 @@
         <v>46387</v>
       </c>
       <c r="E20" t="n">
-        <v>34516345000</v>
+        <v>6712435000</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Satker Besar</t>
+          <t>Satker Sedang</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1619,20 +1619,20 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>A01</t>
+          <t>F00</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>USULAN_DIPA_REVISI</t>
+          <t>REVISI_SABA</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>DIPA-025.01.2.418456/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0055449868353504</t>
+          <t>9554041027073863</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1839,7 @@
         <v>2026</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>45628</v>
+        <v>45334</v>
       </c>
       <c r="E24" t="n">
         <v>36010000</v>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>45628</v>
+        <v>45334</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>2026</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>45992</v>
+        <v>45669</v>
       </c>
       <c r="E26" t="n">
         <v>636800000</v>
@@ -1996,7 +1996,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>45992</v>
+        <v>45669</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>2026</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>46072</v>
+        <v>46360</v>
       </c>
       <c r="E31" t="n">
         <v>2058911000</v>
@@ -2279,12 +2279,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>A02</t>
+          <t>B02</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>USULAN_DIPA_REVISI</t>
+          <t>DIPA_REVISI</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2296,7 +2296,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>46072</v>
+        <v>46360</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>46387</v>
       </c>
       <c r="E32" t="n">
-        <v>3940437000</v>
+        <v>3732709000</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>9312053293800013</t>
+          <t>4010019580019001</t>
         </is>
       </c>
     </row>
@@ -2439,10 +2439,10 @@
         <v>2026</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>46091</v>
+        <v>46387</v>
       </c>
       <c r="E34" t="n">
-        <v>31794415000</v>
+        <v>9005713000</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2459,28 +2459,28 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>B02</t>
+          <t>F00</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>DIPA_REVISI</t>
+          <t>REVISI_SABA</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>DIPA-025.01.2.440502/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>46091</v>
+        <v>46387</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>8130294286711783</t>
+          <t>0264842004608073</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
         <v>2026</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>45628</v>
+        <v>45334</v>
       </c>
       <c r="E39" t="n">
         <v>36010000</v>
@@ -2776,7 +2776,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>45628</v>
+        <v>45334</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>2026</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>45992</v>
+        <v>45991</v>
       </c>
       <c r="E45" t="n">
         <v>448107000</v>
@@ -3119,16 +3119,16 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>B00</t>
+          <t>A01</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>DIPA_AWAL</t>
+          <t>USULAN_DIPA_REVISI</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>45992</v>
+        <v>45991</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>2026</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>45262</v>
+        <v>44969</v>
       </c>
       <c r="E48" t="n">
         <v>2230426000</v>
@@ -3316,7 +3316,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>45262</v>
+        <v>44969</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>2026</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>45262</v>
+        <v>44969</v>
       </c>
       <c r="E50" t="n">
         <v>1660776000</v>
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>45262</v>
+        <v>44969</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>2026</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>45992</v>
+        <v>46178</v>
       </c>
       <c r="E55" t="n">
         <v>1348983000</v>
@@ -3719,16 +3719,16 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>B00</t>
+          <t>B01</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>DIPA_AWAL</t>
+          <t>DIPA_REVISI</t>
         </is>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>45992</v>
+        <v>46178</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>46387</v>
       </c>
       <c r="E58" t="n">
-        <v>47558895000</v>
+        <v>14263923000</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -3899,20 +3899,20 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>A01</t>
+          <t>F00</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>USULAN_DIPA_REVISI</t>
+          <t>REVISI_SABA</t>
         </is>
       </c>
       <c r="K58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>DIPA-025.01.2.666501/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>0702891097600516</t>
+          <t>8711000629708339</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4122,7 @@
         <v>46387</v>
       </c>
       <c r="E62" t="n">
-        <v>348403000</v>
+        <v>60000000</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -4139,20 +4139,20 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>A01</t>
+          <t>F00</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>USULAN_DIPA_REVISI</t>
+          <t>REVISI_SABA</t>
         </is>
       </c>
       <c r="K62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>DIPA-025.07.2.666505/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>3830900165029260</t>
+          <t>0493838984983449</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
         <v>2026</v>
       </c>
       <c r="D63" s="2" t="n">
-        <v>45628</v>
+        <v>45334</v>
       </c>
       <c r="E63" t="n">
         <v>36010000</v>
@@ -4216,7 +4216,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>45628</v>
+        <v>45334</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>46387</v>
       </c>
       <c r="E64" t="n">
-        <v>4067164000</v>
+        <v>3839189000</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>8047070475026798</t>
+          <t>8410967608652918</t>
         </is>
       </c>
     </row>
@@ -4302,7 +4302,7 @@
         <v>46387</v>
       </c>
       <c r="E65" t="n">
-        <v>6520504000</v>
+        <v>6176730000</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>5499650978200792</t>
+          <t>4021309320044735</t>
         </is>
       </c>
     </row>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>669055 - KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR PROV. SUMATRA SELATAN</t>
+          <t>669055 - KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -4602,11 +4602,11 @@
         <v>46387</v>
       </c>
       <c r="E70" t="n">
-        <v>9564537000</v>
+        <v>1455555000</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Satker Besar</t>
+          <t>Satker Kecil</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -4619,20 +4619,20 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>A01</t>
+          <t>F00</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>USULAN_DIPA_REVISI</t>
+          <t>REVISI_SABA</t>
         </is>
       </c>
       <c r="K70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>DIPA-024.03.2.690801/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>0964345706300242</t>
+          <t>0308039672778223</t>
         </is>
       </c>
     </row>

--- a/DATA_DIPA/DIPA_2026.xlsx
+++ b/DATA_DIPA/DIPA_2026.xlsx
@@ -586,7 +586,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Satker Sedang</t>
+          <t>Satker Kecil</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -882,7 +882,7 @@
         <v>46387</v>
       </c>
       <c r="E8" t="n">
-        <v>1067536000</v>
+        <v>517281000</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -899,20 +899,20 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>A01</t>
+          <t>F00</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>USULAN_DIPA_REVISI</t>
+          <t>REVISI_SABA</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>DIPA-066.01.2.111079/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
@@ -920,7 +920,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>7612868030090262</t>
+          <t>8156493671638806</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
         <v>2026</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>44938</v>
+        <v>45261</v>
       </c>
       <c r="E16" t="n">
         <v>6270503000</v>
@@ -1396,7 +1396,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>44938</v>
+        <v>45261</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1479,14 +1479,14 @@
         <v>2026</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>44938</v>
+        <v>45261</v>
       </c>
       <c r="E18" t="n">
         <v>8373512000</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Satker Besar</t>
+          <t>Satker Sedang</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1516,7 +1516,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>44938</v>
+        <v>45261</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>46387</v>
       </c>
       <c r="E20" t="n">
-        <v>6712435000</v>
+        <v>6727044000</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>9554041027073863</t>
+          <t>2700070649321054</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1839,7 @@
         <v>2026</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>45334</v>
+        <v>45628</v>
       </c>
       <c r="E24" t="n">
         <v>36010000</v>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>45334</v>
+        <v>45628</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>2026</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>45669</v>
+        <v>45992</v>
       </c>
       <c r="E26" t="n">
         <v>636800000</v>
@@ -1979,16 +1979,16 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>A01</t>
+          <t>B00</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>USULAN_DIPA_REVISI</t>
+          <t>DIPA_AWAL</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>45669</v>
+        <v>45992</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2259,14 +2259,14 @@
         <v>2026</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>46360</v>
+        <v>46217</v>
       </c>
       <c r="E31" t="n">
         <v>2058911000</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Satker Sedang</t>
+          <t>Satker Kecil</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>B02</t>
+          <t>B03</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>46360</v>
+        <v>46217</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2442,11 +2442,11 @@
         <v>46387</v>
       </c>
       <c r="E34" t="n">
-        <v>9005713000</v>
+        <v>8762036000</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Satker Besar</t>
+          <t>Satker Sedang</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0264842004608073</t>
+          <t>9500011907817588</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
         <v>2026</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>45334</v>
+        <v>45628</v>
       </c>
       <c r="E39" t="n">
         <v>36010000</v>
@@ -2776,7 +2776,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>45334</v>
+        <v>45628</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>2026</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>46076</v>
+        <v>46217</v>
       </c>
       <c r="E44" t="n">
         <v>758536000</v>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>B01</t>
+          <t>B02</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3068,7 +3068,7 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>46076</v>
+        <v>46217</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>2026</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>45991</v>
+        <v>46213</v>
       </c>
       <c r="E45" t="n">
         <v>448107000</v>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>A01</t>
+          <t>B01</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>USULAN_DIPA_REVISI</t>
+          <t>DIPA_REVISI</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>45991</v>
+        <v>46213</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>2026</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>44969</v>
+        <v>45262</v>
       </c>
       <c r="E48" t="n">
         <v>2230426000</v>
@@ -3316,7 +3316,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>44969</v>
+        <v>45262</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>2026</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>44969</v>
+        <v>45262</v>
       </c>
       <c r="E50" t="n">
         <v>1660776000</v>
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>44969</v>
+        <v>45262</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>656553 - KPU  KABUPATEN OGAN KOMERING ULU</t>
+          <t>656553 - KPU KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>656560 - KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>656560 - KPU KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>656574 - KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>656574 - KPU KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -3699,7 +3699,7 @@
         <v>2026</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>46178</v>
+        <v>46218</v>
       </c>
       <c r="E55" t="n">
         <v>1348983000</v>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>B01</t>
+          <t>B02</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="K55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>46178</v>
+        <v>46218</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>46387</v>
       </c>
       <c r="E58" t="n">
-        <v>14263923000</v>
+        <v>13991110000</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>8711000629708339</t>
+          <t>0009047369801775</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
         <v>2026</v>
       </c>
       <c r="D63" s="2" t="n">
-        <v>45334</v>
+        <v>45628</v>
       </c>
       <c r="E63" t="n">
         <v>36010000</v>
@@ -4216,7 +4216,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>45334</v>
+        <v>45628</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>46387</v>
       </c>
       <c r="E70" t="n">
-        <v>1455555000</v>
+        <v>312702000</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>F00</t>
+          <t>F01</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>0308039672778223</t>
+          <t>5008376858341992</t>
         </is>
       </c>
     </row>
